--- a/data/Test1_Belgique.xlsx
+++ b/data/Test1_Belgique.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://digiplace-my.sharepoint.com/personal/aurelien_brun_wavestone_com/Documents/Desktop/mapper/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_F25DC773A252ABDACC1048BDC11F63425BDE58E3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C69326E0-DE3B-454A-BCD1-EC1C5DC1E0CF}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_F25DC773A252ABDACC1048BDC11F63425BDE58E3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F211758-80CC-412C-8647-93D0BC0CA5F7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="58">
   <si>
     <t>Title</t>
   </si>
@@ -193,13 +193,19 @@
   </si>
   <si>
     <t xml:space="preserve"> Privileged users shall be qualified before privileges are granted, and these users shall be able to demonstrate an understanding of their roles, responsibilities, and authorities.</t>
+  </si>
+  <si>
+    <t>Important</t>
+  </si>
+  <si>
+    <t>Essential</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,6 +220,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -223,11 +235,20 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -236,13 +257,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -525,10 +552,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -541,8 +568,14 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -555,8 +588,14 @@
       <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -569,8 +608,14 @@
       <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F3" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -583,8 +628,14 @@
       <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -597,8 +648,14 @@
       <c r="D5" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F5" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -611,8 +668,14 @@
       <c r="D6" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -625,8 +688,14 @@
       <c r="D7" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
@@ -639,8 +708,14 @@
       <c r="D8" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -653,8 +728,14 @@
       <c r="D9" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -667,8 +748,14 @@
       <c r="D10" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
@@ -681,8 +768,14 @@
       <c r="D11" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>34</v>
       </c>
@@ -695,8 +788,14 @@
       <c r="D12" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>38</v>
       </c>
@@ -709,8 +808,14 @@
       <c r="D13" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>41</v>
       </c>
@@ -723,8 +828,14 @@
       <c r="D14" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F14" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>44</v>
       </c>
@@ -737,8 +848,14 @@
       <c r="D15" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>47</v>
       </c>
@@ -751,8 +868,14 @@
       <c r="D16" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>50</v>
       </c>
@@ -765,8 +888,14 @@
       <c r="D17" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>53</v>
       </c>
@@ -778,6 +907,12 @@
       </c>
       <c r="D18" s="2" t="s">
         <v>55</v>
+      </c>
+      <c r="F18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
